--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DOCKER AND KUBERNETES FOUNDATION/Docker Vs.VM/docker_vs_vm.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DOCKER AND KUBERNETES FOUNDATION/Docker Vs.VM/docker_vs_vm.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docker Vs VM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OS</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>kernel</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>guest</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>milliseconds</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>hypervisor</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Docker (no duplicate OS overhead)</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stronger</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>No (kernel mismatch)</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
